--- a/data/workouts.xlsx
+++ b/data/workouts.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="seances" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="exercices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="calendrier" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="seances" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="exercices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="calendrier" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2755,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
         <v>105</v>
@@ -2778,7 +2778,7 @@
         <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E101" t="n">
         <v>80</v>
@@ -2801,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E102" t="n">
         <v>8</v>
@@ -2824,7 +2824,7 @@
         <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E103" t="n">
         <v>9</v>
@@ -2847,7 +2847,7 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E104" t="n">
         <v>26</v>
@@ -2870,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E105" t="n">
         <v>28</v>
@@ -2893,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E106" t="n">
         <v>12</v>
@@ -2916,7 +2916,7 @@
         <v>2</v>
       </c>
       <c r="D107" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E107" t="n">
         <v>11</v>
@@ -2939,7 +2939,7 @@
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E108" t="n">
         <v>67.5</v>
@@ -2962,7 +2962,7 @@
         <v>2</v>
       </c>
       <c r="D109" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E109" t="n">
         <v>62.5</v>
@@ -2989,7 +2989,7 @@
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E110" t="n">
         <v>60</v>
@@ -3012,7 +3012,7 @@
         <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E111" t="n">
         <v>52.5</v>
@@ -3035,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E112" t="n">
         <v>13</v>
@@ -3058,7 +3058,7 @@
         <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E113" t="n">
         <v>13</v>
@@ -3081,7 +3081,7 @@
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E114" t="n">
         <v>52.5</v>
@@ -3104,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E115" t="n">
         <v>45</v>
@@ -3127,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E116" t="n">
         <v>21</v>
@@ -3150,7 +3150,7 @@
         <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E117" t="n">
         <v>23</v>
@@ -3173,7 +3173,7 @@
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E118" t="n">
         <v>72.5</v>
@@ -3196,7 +3196,7 @@
         <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E119" t="n">
         <v>70</v>
@@ -3219,7 +3219,7 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E120" t="n">
         <v>55</v>
@@ -3246,7 +3246,7 @@
         <v>2</v>
       </c>
       <c r="D121" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E121" t="n">
         <v>55</v>
@@ -3269,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E122" t="n">
         <v>13</v>
@@ -3292,7 +3292,7 @@
         <v>2</v>
       </c>
       <c r="D123" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E123" t="n">
         <v>13</v>
@@ -3315,7 +3315,7 @@
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E124" t="n">
         <v>47.5</v>
@@ -3338,7 +3338,7 @@
         <v>2</v>
       </c>
       <c r="D125" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
         <v>45</v>
@@ -3361,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E126" t="n">
         <v>27</v>
@@ -3384,7 +3384,7 @@
         <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E127" t="n">
         <v>20</v>
@@ -6455,7 +6455,7 @@
         <v>1</v>
       </c>
       <c r="D260" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E260" t="n">
         <v>95</v>
@@ -6478,7 +6478,7 @@
         <v>2</v>
       </c>
       <c r="D261" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E261" t="n">
         <v>97.5</v>
@@ -6501,7 +6501,7 @@
         <v>1</v>
       </c>
       <c r="D262" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E262" t="n">
         <v>8</v>
@@ -6524,7 +6524,7 @@
         <v>2</v>
       </c>
       <c r="D263" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E263" t="n">
         <v>11</v>
@@ -6547,7 +6547,7 @@
         <v>1</v>
       </c>
       <c r="D264" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E264" t="n">
         <v>30</v>
@@ -6570,7 +6570,7 @@
         <v>2</v>
       </c>
       <c r="D265" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E265" t="n">
         <v>28</v>
@@ -6593,7 +6593,7 @@
         <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E266" t="n">
         <v>12</v>
@@ -6620,7 +6620,7 @@
         <v>2</v>
       </c>
       <c r="D267" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E267" t="n">
         <v>11</v>
@@ -6643,7 +6643,7 @@
         <v>1</v>
       </c>
       <c r="D268" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E268" t="n">
         <v>72.5</v>
@@ -6666,7 +6666,7 @@
         <v>2</v>
       </c>
       <c r="D269" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E269" t="n">
         <v>67.5</v>
@@ -6689,7 +6689,7 @@
         <v>1</v>
       </c>
       <c r="D270" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E270" t="n">
         <v>65</v>
@@ -6712,7 +6712,7 @@
         <v>2</v>
       </c>
       <c r="D271" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E271" t="n">
         <v>55</v>
@@ -6735,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="D272" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E272" t="n">
         <v>14</v>
@@ -6758,7 +6758,7 @@
         <v>2</v>
       </c>
       <c r="D273" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E273" t="n">
         <v>13</v>
@@ -6781,7 +6781,7 @@
         <v>1</v>
       </c>
       <c r="D274" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E274" t="n">
         <v>45</v>
@@ -6804,7 +6804,7 @@
         <v>2</v>
       </c>
       <c r="D275" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E275" t="n">
         <v>45</v>
@@ -6827,7 +6827,7 @@
         <v>1</v>
       </c>
       <c r="D276" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E276" t="n">
         <v>24</v>
@@ -6850,7 +6850,7 @@
         <v>2</v>
       </c>
       <c r="D277" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E277" t="n">
         <v>23</v>
@@ -6873,7 +6873,7 @@
         <v>1</v>
       </c>
       <c r="D278" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E278" t="n">
         <v>102.5</v>
@@ -6896,7 +6896,7 @@
         <v>2</v>
       </c>
       <c r="D279" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E279" t="n">
         <v>97.5</v>
@@ -6919,7 +6919,7 @@
         <v>1</v>
       </c>
       <c r="D280" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E280" t="n">
         <v>9</v>
@@ -6942,7 +6942,7 @@
         <v>2</v>
       </c>
       <c r="D281" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E281" t="n">
         <v>9</v>
@@ -6965,7 +6965,7 @@
         <v>1</v>
       </c>
       <c r="D282" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E282" t="n">
         <v>26</v>
@@ -6988,7 +6988,7 @@
         <v>2</v>
       </c>
       <c r="D283" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E283" t="n">
         <v>27</v>
@@ -7011,7 +7011,7 @@
         <v>1</v>
       </c>
       <c r="D284" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E284" t="n">
         <v>12</v>
@@ -7034,7 +7034,7 @@
         <v>2</v>
       </c>
       <c r="D285" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E285" t="n">
         <v>11</v>
@@ -7057,7 +7057,7 @@
         <v>1</v>
       </c>
       <c r="D286" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E286" t="n">
         <v>95</v>
@@ -7080,7 +7080,7 @@
         <v>2</v>
       </c>
       <c r="D287" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E287" t="n">
         <v>97.5</v>
@@ -7103,7 +7103,7 @@
         <v>1</v>
       </c>
       <c r="D288" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E288" t="n">
         <v>87.5</v>
@@ -7126,7 +7126,7 @@
         <v>2</v>
       </c>
       <c r="D289" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E289" t="n">
         <v>77.5</v>
@@ -7153,7 +7153,7 @@
         <v>1</v>
       </c>
       <c r="D290" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E290" t="n">
         <v>157.5</v>
@@ -7180,7 +7180,7 @@
         <v>2</v>
       </c>
       <c r="D291" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E291" t="n">
         <v>147.5</v>
@@ -7203,7 +7203,7 @@
         <v>1</v>
       </c>
       <c r="D292" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E292" t="n">
         <v>47.5</v>
@@ -7226,7 +7226,7 @@
         <v>2</v>
       </c>
       <c r="D293" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E293" t="n">
         <v>37.5</v>
@@ -7249,7 +7249,7 @@
         <v>1</v>
       </c>
       <c r="D294" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E294" t="n">
         <v>70</v>
@@ -7272,7 +7272,7 @@
         <v>2</v>
       </c>
       <c r="D295" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E295" t="n">
         <v>65</v>
@@ -7295,7 +7295,7 @@
         <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E296" t="n">
         <v>62.5</v>
@@ -7318,7 +7318,7 @@
         <v>2</v>
       </c>
       <c r="D297" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E297" t="n">
         <v>55</v>
@@ -7341,7 +7341,7 @@
         <v>1</v>
       </c>
       <c r="D298" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E298" t="n">
         <v>14</v>
@@ -7364,7 +7364,7 @@
         <v>2</v>
       </c>
       <c r="D299" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E299" t="n">
         <v>13</v>
@@ -7387,7 +7387,7 @@
         <v>1</v>
       </c>
       <c r="D300" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E300" t="n">
         <v>52.5</v>
@@ -7410,7 +7410,7 @@
         <v>2</v>
       </c>
       <c r="D301" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E301" t="n">
         <v>47.5</v>
@@ -7433,7 +7433,7 @@
         <v>1</v>
       </c>
       <c r="D302" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E302" t="n">
         <v>23</v>
@@ -7456,7 +7456,7 @@
         <v>2</v>
       </c>
       <c r="D303" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E303" t="n">
         <v>25</v>
@@ -10079,7 +10079,7 @@
         <v>1</v>
       </c>
       <c r="D416" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E416" t="n">
         <v>105</v>
@@ -10102,7 +10102,7 @@
         <v>2</v>
       </c>
       <c r="D417" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E417" t="n">
         <v>105</v>
@@ -10125,7 +10125,7 @@
         <v>1</v>
       </c>
       <c r="D418" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E418" t="n">
         <v>12</v>
@@ -10148,7 +10148,7 @@
         <v>2</v>
       </c>
       <c r="D419" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E419" t="n">
         <v>10</v>
@@ -10175,7 +10175,7 @@
         <v>1</v>
       </c>
       <c r="D420" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E420" t="n">
         <v>27</v>
@@ -10198,7 +10198,7 @@
         <v>2</v>
       </c>
       <c r="D421" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E421" t="n">
         <v>28</v>
@@ -10221,7 +10221,7 @@
         <v>1</v>
       </c>
       <c r="D422" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E422" t="n">
         <v>12</v>
@@ -10244,7 +10244,7 @@
         <v>2</v>
       </c>
       <c r="D423" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E423" t="n">
         <v>12</v>
@@ -10267,7 +10267,7 @@
         <v>1</v>
       </c>
       <c r="D424" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E424" t="n">
         <v>75</v>
@@ -10290,7 +10290,7 @@
         <v>2</v>
       </c>
       <c r="D425" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E425" t="n">
         <v>72.5</v>
@@ -10313,7 +10313,7 @@
         <v>1</v>
       </c>
       <c r="D426" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E426" t="n">
         <v>60</v>
@@ -10336,7 +10336,7 @@
         <v>2</v>
       </c>
       <c r="D427" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E427" t="n">
         <v>57.5</v>
@@ -10359,7 +10359,7 @@
         <v>1</v>
       </c>
       <c r="D428" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E428" t="n">
         <v>14</v>
@@ -10382,7 +10382,7 @@
         <v>2</v>
       </c>
       <c r="D429" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E429" t="n">
         <v>14</v>
@@ -10405,7 +10405,7 @@
         <v>1</v>
       </c>
       <c r="D430" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E430" t="n">
         <v>50</v>
@@ -10428,7 +10428,7 @@
         <v>2</v>
       </c>
       <c r="D431" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E431" t="n">
         <v>47.5</v>
@@ -10451,7 +10451,7 @@
         <v>1</v>
       </c>
       <c r="D432" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E432" t="n">
         <v>26</v>
@@ -10474,7 +10474,7 @@
         <v>2</v>
       </c>
       <c r="D433" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E433" t="n">
         <v>26</v>
@@ -10501,7 +10501,7 @@
         <v>1</v>
       </c>
       <c r="D434" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E434" t="n">
         <v>107.5</v>
@@ -10524,7 +10524,7 @@
         <v>2</v>
       </c>
       <c r="D435" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E435" t="n">
         <v>105</v>
@@ -10547,7 +10547,7 @@
         <v>1</v>
       </c>
       <c r="D436" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E436" t="n">
         <v>11</v>
@@ -10570,7 +10570,7 @@
         <v>2</v>
       </c>
       <c r="D437" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E437" t="n">
         <v>9</v>
@@ -10593,7 +10593,7 @@
         <v>1</v>
       </c>
       <c r="D438" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E438" t="n">
         <v>32.5</v>
@@ -10616,7 +10616,7 @@
         <v>2</v>
       </c>
       <c r="D439" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E439" t="n">
         <v>28</v>
@@ -10639,7 +10639,7 @@
         <v>1</v>
       </c>
       <c r="D440" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E440" t="n">
         <v>13</v>
@@ -10662,7 +10662,7 @@
         <v>2</v>
       </c>
       <c r="D441" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E441" t="n">
         <v>12</v>
@@ -10685,7 +10685,7 @@
         <v>1</v>
       </c>
       <c r="D442" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E442" t="n">
         <v>97.5</v>
@@ -10708,7 +10708,7 @@
         <v>2</v>
       </c>
       <c r="D443" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E443" t="n">
         <v>97.5</v>
@@ -10731,7 +10731,7 @@
         <v>1</v>
       </c>
       <c r="D444" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E444" t="n">
         <v>90</v>
@@ -10754,7 +10754,7 @@
         <v>2</v>
       </c>
       <c r="D445" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E445" t="n">
         <v>85</v>
@@ -10777,7 +10777,7 @@
         <v>1</v>
       </c>
       <c r="D446" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E446" t="n">
         <v>135</v>
@@ -10800,7 +10800,7 @@
         <v>2</v>
       </c>
       <c r="D447" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E447" t="n">
         <v>135</v>
@@ -10823,7 +10823,7 @@
         <v>1</v>
       </c>
       <c r="D448" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E448" t="n">
         <v>45</v>
@@ -10846,7 +10846,7 @@
         <v>2</v>
       </c>
       <c r="D449" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E449" t="n">
         <v>42.5</v>
@@ -10869,7 +10869,7 @@
         <v>1</v>
       </c>
       <c r="D450" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E450" t="n">
         <v>70</v>
@@ -10892,7 +10892,7 @@
         <v>2</v>
       </c>
       <c r="D451" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E451" t="n">
         <v>75</v>
@@ -10915,7 +10915,7 @@
         <v>1</v>
       </c>
       <c r="D452" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E452" t="n">
         <v>60</v>
@@ -10938,7 +10938,7 @@
         <v>2</v>
       </c>
       <c r="D453" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E453" t="n">
         <v>60</v>
@@ -10961,7 +10961,7 @@
         <v>1</v>
       </c>
       <c r="D454" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E454" t="n">
         <v>15</v>
@@ -10984,7 +10984,7 @@
         <v>2</v>
       </c>
       <c r="D455" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E455" t="n">
         <v>14</v>
@@ -11011,7 +11011,7 @@
         <v>1</v>
       </c>
       <c r="D456" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E456" t="n">
         <v>47.5</v>
@@ -11034,7 +11034,7 @@
         <v>2</v>
       </c>
       <c r="D457" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E457" t="n">
         <v>47.5</v>
@@ -11057,7 +11057,7 @@
         <v>1</v>
       </c>
       <c r="D458" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E458" t="n">
         <v>23</v>
@@ -11080,7 +11080,7 @@
         <v>2</v>
       </c>
       <c r="D459" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E459" t="n">
         <v>24</v>
@@ -13561,7 +13561,7 @@
         <v>1</v>
       </c>
       <c r="D566" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E566" t="n">
         <v>77.5</v>
@@ -13584,7 +13584,7 @@
         <v>2</v>
       </c>
       <c r="D567" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E567" t="n">
         <v>75</v>
@@ -13611,7 +13611,7 @@
         <v>1</v>
       </c>
       <c r="D568" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E568" t="n">
         <v>57.5</v>
@@ -13634,7 +13634,7 @@
         <v>2</v>
       </c>
       <c r="D569" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E569" t="n">
         <v>55</v>
@@ -13657,7 +13657,7 @@
         <v>1</v>
       </c>
       <c r="D570" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E570" t="n">
         <v>15</v>
@@ -13680,7 +13680,7 @@
         <v>2</v>
       </c>
       <c r="D571" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E571" t="n">
         <v>15</v>
@@ -13703,7 +13703,7 @@
         <v>1</v>
       </c>
       <c r="D572" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E572" t="n">
         <v>50</v>
@@ -13726,7 +13726,7 @@
         <v>2</v>
       </c>
       <c r="D573" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E573" t="n">
         <v>52.5</v>
@@ -13749,7 +13749,7 @@
         <v>1</v>
       </c>
       <c r="D574" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E574" t="n">
         <v>27</v>
@@ -13772,7 +13772,7 @@
         <v>2</v>
       </c>
       <c r="D575" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E575" t="n">
         <v>22</v>
@@ -13795,7 +13795,7 @@
         <v>1</v>
       </c>
       <c r="D576" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E576" t="n">
         <v>100</v>
@@ -13818,7 +13818,7 @@
         <v>2</v>
       </c>
       <c r="D577" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E577" t="n">
         <v>97.5</v>
@@ -13841,7 +13841,7 @@
         <v>1</v>
       </c>
       <c r="D578" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E578" t="n">
         <v>11</v>
@@ -13864,7 +13864,7 @@
         <v>2</v>
       </c>
       <c r="D579" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E579" t="n">
         <v>10</v>
@@ -13887,7 +13887,7 @@
         <v>1</v>
       </c>
       <c r="D580" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E580" t="n">
         <v>29</v>
@@ -13910,7 +13910,7 @@
         <v>2</v>
       </c>
       <c r="D581" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E581" t="n">
         <v>35</v>
@@ -13933,7 +13933,7 @@
         <v>1</v>
       </c>
       <c r="D582" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E582" t="n">
         <v>13</v>
@@ -13956,7 +13956,7 @@
         <v>2</v>
       </c>
       <c r="D583" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E583" t="n">
         <v>12</v>
@@ -13979,7 +13979,7 @@
         <v>1</v>
       </c>
       <c r="D584" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E584" t="n">
         <v>95</v>
@@ -14002,7 +14002,7 @@
         <v>2</v>
       </c>
       <c r="D585" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E585" t="n">
         <v>100</v>
@@ -14025,7 +14025,7 @@
         <v>1</v>
       </c>
       <c r="D586" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E586" t="n">
         <v>95</v>
@@ -14048,7 +14048,7 @@
         <v>2</v>
       </c>
       <c r="D587" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E587" t="n">
         <v>90</v>
@@ -14071,7 +14071,7 @@
         <v>1</v>
       </c>
       <c r="D588" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E588" t="n">
         <v>137.5</v>
@@ -14094,7 +14094,7 @@
         <v>2</v>
       </c>
       <c r="D589" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E589" t="n">
         <v>157.5</v>
@@ -14117,7 +14117,7 @@
         <v>1</v>
       </c>
       <c r="D590" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E590" t="n">
         <v>45</v>
@@ -14140,7 +14140,7 @@
         <v>2</v>
       </c>
       <c r="D591" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E591" t="n">
         <v>40</v>
@@ -14163,7 +14163,7 @@
         <v>1</v>
       </c>
       <c r="D592" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E592" t="n">
         <v>72.5</v>
@@ -14186,7 +14186,7 @@
         <v>2</v>
       </c>
       <c r="D593" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E593" t="n">
         <v>77.5</v>
@@ -14209,7 +14209,7 @@
         <v>1</v>
       </c>
       <c r="D594" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E594" t="n">
         <v>57.5</v>
@@ -14232,7 +14232,7 @@
         <v>2</v>
       </c>
       <c r="D595" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E595" t="n">
         <v>60</v>
@@ -14255,7 +14255,7 @@
         <v>1</v>
       </c>
       <c r="D596" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E596" t="n">
         <v>15</v>
@@ -14278,7 +14278,7 @@
         <v>2</v>
       </c>
       <c r="D597" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E597" t="n">
         <v>15</v>
@@ -14301,7 +14301,7 @@
         <v>1</v>
       </c>
       <c r="D598" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E598" t="n">
         <v>47.5</v>
@@ -14324,7 +14324,7 @@
         <v>2</v>
       </c>
       <c r="D599" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E599" t="n">
         <v>52.5</v>
@@ -14347,7 +14347,7 @@
         <v>1</v>
       </c>
       <c r="D600" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E600" t="n">
         <v>26</v>
@@ -14370,7 +14370,7 @@
         <v>2</v>
       </c>
       <c r="D601" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E601" t="n">
         <v>25</v>
@@ -16437,7 +16437,7 @@
         <v>1</v>
       </c>
       <c r="D690" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E690" t="n">
         <v>107.5</v>
@@ -16460,7 +16460,7 @@
         <v>2</v>
       </c>
       <c r="D691" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E691" t="n">
         <v>102.5</v>
@@ -16483,7 +16483,7 @@
         <v>1</v>
       </c>
       <c r="D692" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E692" t="n">
         <v>14</v>
@@ -16506,7 +16506,7 @@
         <v>2</v>
       </c>
       <c r="D693" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E693" t="n">
         <v>11</v>
@@ -16529,7 +16529,7 @@
         <v>1</v>
       </c>
       <c r="D694" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E694" t="n">
         <v>30</v>
@@ -16552,7 +16552,7 @@
         <v>2</v>
       </c>
       <c r="D695" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E695" t="n">
         <v>28</v>
@@ -16575,7 +16575,7 @@
         <v>1</v>
       </c>
       <c r="D696" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E696" t="n">
         <v>13</v>
@@ -16598,7 +16598,7 @@
         <v>2</v>
       </c>
       <c r="D697" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E697" t="n">
         <v>13</v>
@@ -16621,7 +16621,7 @@
         <v>1</v>
       </c>
       <c r="D698" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E698" t="n">
         <v>80</v>
@@ -16644,7 +16644,7 @@
         <v>2</v>
       </c>
       <c r="D699" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E699" t="n">
         <v>72.5</v>
@@ -16667,7 +16667,7 @@
         <v>1</v>
       </c>
       <c r="D700" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E700" t="n">
         <v>62.5</v>
@@ -16690,7 +16690,7 @@
         <v>2</v>
       </c>
       <c r="D701" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E701" t="n">
         <v>60</v>
@@ -16713,7 +16713,7 @@
         <v>1</v>
       </c>
       <c r="D702" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E702" t="n">
         <v>15</v>
@@ -16736,7 +16736,7 @@
         <v>2</v>
       </c>
       <c r="D703" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E703" t="n">
         <v>15</v>
@@ -16759,7 +16759,7 @@
         <v>1</v>
       </c>
       <c r="D704" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E704" t="n">
         <v>50</v>
@@ -16782,7 +16782,7 @@
         <v>2</v>
       </c>
       <c r="D705" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E705" t="n">
         <v>50</v>
@@ -16805,7 +16805,7 @@
         <v>1</v>
       </c>
       <c r="D706" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E706" t="n">
         <v>25</v>
@@ -16828,7 +16828,7 @@
         <v>2</v>
       </c>
       <c r="D707" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E707" t="n">
         <v>22</v>
@@ -16851,7 +16851,7 @@
         <v>1</v>
       </c>
       <c r="D708" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E708" t="n">
         <v>92.5</v>
@@ -16874,7 +16874,7 @@
         <v>2</v>
       </c>
       <c r="D709" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E709" t="n">
         <v>97.5</v>
@@ -16897,7 +16897,7 @@
         <v>1</v>
       </c>
       <c r="D710" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E710" t="n">
         <v>14</v>
@@ -16920,7 +16920,7 @@
         <v>2</v>
       </c>
       <c r="D711" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E711" t="n">
         <v>12</v>
@@ -16943,7 +16943,7 @@
         <v>1</v>
       </c>
       <c r="D712" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E712" t="n">
         <v>30</v>
@@ -16966,7 +16966,7 @@
         <v>2</v>
       </c>
       <c r="D713" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E713" t="n">
         <v>29</v>
@@ -16989,7 +16989,7 @@
         <v>1</v>
       </c>
       <c r="D714" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E714" t="n">
         <v>13</v>
@@ -17012,7 +17012,7 @@
         <v>2</v>
       </c>
       <c r="D715" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E715" t="n">
         <v>13</v>
@@ -17035,7 +17035,7 @@
         <v>1</v>
       </c>
       <c r="D716" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E716" t="n">
         <v>107.5</v>
@@ -17058,7 +17058,7 @@
         <v>2</v>
       </c>
       <c r="D717" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E717" t="n">
         <v>102.5</v>
@@ -17085,7 +17085,7 @@
         <v>1</v>
       </c>
       <c r="D718" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E718" t="n">
         <v>90</v>
@@ -17108,7 +17108,7 @@
         <v>2</v>
       </c>
       <c r="D719" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E719" t="n">
         <v>90</v>
@@ -17131,7 +17131,7 @@
         <v>1</v>
       </c>
       <c r="D720" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E720" t="n">
         <v>135</v>
@@ -17154,7 +17154,7 @@
         <v>2</v>
       </c>
       <c r="D721" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E721" t="n">
         <v>142.5</v>
@@ -17177,7 +17177,7 @@
         <v>1</v>
       </c>
       <c r="D722" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E722" t="n">
         <v>47.5</v>
@@ -17200,7 +17200,7 @@
         <v>2</v>
       </c>
       <c r="D723" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E723" t="n">
         <v>42.5</v>
@@ -17223,7 +17223,7 @@
         <v>1</v>
       </c>
       <c r="D724" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E724" t="n">
         <v>77.5</v>
@@ -17246,7 +17246,7 @@
         <v>2</v>
       </c>
       <c r="D725" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E725" t="n">
         <v>80</v>
@@ -17269,7 +17269,7 @@
         <v>1</v>
       </c>
       <c r="D726" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E726" t="n">
         <v>57.5</v>
@@ -17292,7 +17292,7 @@
         <v>2</v>
       </c>
       <c r="D727" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E727" t="n">
         <v>62.5</v>
@@ -17315,7 +17315,7 @@
         <v>1</v>
       </c>
       <c r="D728" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E728" t="n">
         <v>15</v>
@@ -17338,7 +17338,7 @@
         <v>2</v>
       </c>
       <c r="D729" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E729" t="n">
         <v>15</v>
@@ -17361,7 +17361,7 @@
         <v>1</v>
       </c>
       <c r="D730" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E730" t="n">
         <v>55</v>
@@ -17384,7 +17384,7 @@
         <v>2</v>
       </c>
       <c r="D731" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E731" t="n">
         <v>47.5</v>
@@ -17407,7 +17407,7 @@
         <v>1</v>
       </c>
       <c r="D732" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E732" t="n">
         <v>25</v>
@@ -17430,7 +17430,7 @@
         <v>2</v>
       </c>
       <c r="D733" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E733" t="n">
         <v>28</v>
@@ -20287,7 +20287,7 @@
         <v>1</v>
       </c>
       <c r="D856" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E856" t="n">
         <v>105</v>
@@ -20310,7 +20310,7 @@
         <v>2</v>
       </c>
       <c r="D857" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E857" t="n">
         <v>110</v>
@@ -20333,7 +20333,7 @@
         <v>1</v>
       </c>
       <c r="D858" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E858" t="n">
         <v>13</v>
@@ -20356,7 +20356,7 @@
         <v>2</v>
       </c>
       <c r="D859" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E859" t="n">
         <v>12</v>
@@ -20379,7 +20379,7 @@
         <v>1</v>
       </c>
       <c r="D860" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E860" t="n">
         <v>29</v>
@@ -20402,7 +20402,7 @@
         <v>2</v>
       </c>
       <c r="D861" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E861" t="n">
         <v>30</v>
@@ -20425,7 +20425,7 @@
         <v>1</v>
       </c>
       <c r="D862" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E862" t="n">
         <v>13</v>
@@ -20448,7 +20448,7 @@
         <v>2</v>
       </c>
       <c r="D863" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E863" t="n">
         <v>14</v>
@@ -20471,7 +20471,7 @@
         <v>1</v>
       </c>
       <c r="D864" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E864" t="n">
         <v>82.5</v>
@@ -20494,7 +20494,7 @@
         <v>2</v>
       </c>
       <c r="D865" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E865" t="n">
         <v>80</v>
@@ -20517,7 +20517,7 @@
         <v>1</v>
       </c>
       <c r="D866" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E866" t="n">
         <v>65</v>
@@ -20540,7 +20540,7 @@
         <v>2</v>
       </c>
       <c r="D867" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E867" t="n">
         <v>60</v>
@@ -20563,7 +20563,7 @@
         <v>1</v>
       </c>
       <c r="D868" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E868" t="n">
         <v>16</v>
@@ -20586,7 +20586,7 @@
         <v>2</v>
       </c>
       <c r="D869" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E869" t="n">
         <v>15</v>
@@ -20609,7 +20609,7 @@
         <v>1</v>
       </c>
       <c r="D870" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E870" t="n">
         <v>57.5</v>
@@ -20632,7 +20632,7 @@
         <v>2</v>
       </c>
       <c r="D871" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E871" t="n">
         <v>50</v>
@@ -20655,7 +20655,7 @@
         <v>1</v>
       </c>
       <c r="D872" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E872" t="n">
         <v>26</v>
@@ -20678,7 +20678,7 @@
         <v>2</v>
       </c>
       <c r="D873" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E873" t="n">
         <v>25</v>
@@ -20701,7 +20701,7 @@
         <v>1</v>
       </c>
       <c r="D874" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E874" t="n">
         <v>112.5</v>
@@ -20724,7 +20724,7 @@
         <v>2</v>
       </c>
       <c r="D875" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E875" t="n">
         <v>107.5</v>
@@ -20751,7 +20751,7 @@
         <v>1</v>
       </c>
       <c r="D876" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E876" t="n">
         <v>11</v>
@@ -20778,7 +20778,7 @@
         <v>2</v>
       </c>
       <c r="D877" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E877" t="n">
         <v>12</v>
@@ -20801,7 +20801,7 @@
         <v>1</v>
       </c>
       <c r="D878" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E878" t="n">
         <v>32.5</v>
@@ -20824,7 +20824,7 @@
         <v>2</v>
       </c>
       <c r="D879" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E879" t="n">
         <v>32.5</v>
@@ -20847,7 +20847,7 @@
         <v>1</v>
       </c>
       <c r="D880" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E880" t="n">
         <v>14</v>
@@ -20874,7 +20874,7 @@
         <v>2</v>
       </c>
       <c r="D881" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E881" t="n">
         <v>13</v>
@@ -20897,7 +20897,7 @@
         <v>1</v>
       </c>
       <c r="D882" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E882" t="n">
         <v>107.5</v>
@@ -20920,7 +20920,7 @@
         <v>2</v>
       </c>
       <c r="D883" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E883" t="n">
         <v>110</v>
@@ -20943,7 +20943,7 @@
         <v>1</v>
       </c>
       <c r="D884" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E884" t="n">
         <v>100</v>
@@ -20966,7 +20966,7 @@
         <v>2</v>
       </c>
       <c r="D885" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E885" t="n">
         <v>100</v>
@@ -20989,7 +20989,7 @@
         <v>1</v>
       </c>
       <c r="D886" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E886" t="n">
         <v>150</v>
@@ -21012,7 +21012,7 @@
         <v>2</v>
       </c>
       <c r="D887" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E887" t="n">
         <v>147.5</v>
@@ -21035,7 +21035,7 @@
         <v>1</v>
       </c>
       <c r="D888" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E888" t="n">
         <v>47.5</v>
@@ -21058,7 +21058,7 @@
         <v>2</v>
       </c>
       <c r="D889" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E889" t="n">
         <v>45</v>
@@ -21081,7 +21081,7 @@
         <v>1</v>
       </c>
       <c r="D890" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E890" t="n">
         <v>80</v>
@@ -21104,7 +21104,7 @@
         <v>2</v>
       </c>
       <c r="D891" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E891" t="n">
         <v>80</v>
@@ -21127,7 +21127,7 @@
         <v>1</v>
       </c>
       <c r="D892" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E892" t="n">
         <v>62.5</v>
@@ -21150,7 +21150,7 @@
         <v>2</v>
       </c>
       <c r="D893" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E893" t="n">
         <v>65</v>
@@ -21173,7 +21173,7 @@
         <v>1</v>
       </c>
       <c r="D894" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E894" t="n">
         <v>16</v>
@@ -21196,7 +21196,7 @@
         <v>2</v>
       </c>
       <c r="D895" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E895" t="n">
         <v>16</v>
@@ -21219,7 +21219,7 @@
         <v>1</v>
       </c>
       <c r="D896" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E896" t="n">
         <v>52.5</v>
@@ -21242,7 +21242,7 @@
         <v>2</v>
       </c>
       <c r="D897" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E897" t="n">
         <v>55</v>
@@ -21265,7 +21265,7 @@
         <v>1</v>
       </c>
       <c r="D898" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E898" t="n">
         <v>27</v>
@@ -21288,7 +21288,7 @@
         <v>2</v>
       </c>
       <c r="D899" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E899" t="n">
         <v>24</v>
@@ -23152,7 +23152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:D182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23163,27 +23163,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>semaine</t>
+          <t>semaine_programme</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>semaine_programme</t>
+          <t>mois</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>mois</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>annee</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>jour_semaine</t>
         </is>
       </c>
     </row>
@@ -23192,21 +23182,13 @@
         <v>45962</v>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E2" t="n">
         <v>2025</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -23214,21 +23196,13 @@
         <v>45963</v>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E3" t="n">
         <v>2025</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -23236,21 +23210,13 @@
         <v>45964</v>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E4" t="n">
         <v>2025</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -23258,21 +23224,13 @@
         <v>45965</v>
       </c>
       <c r="B5" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E5" t="n">
         <v>2025</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -23280,21 +23238,13 @@
         <v>45966</v>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
-      </c>
-      <c r="E6" t="n">
         <v>2025</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -23302,21 +23252,13 @@
         <v>45967</v>
       </c>
       <c r="B7" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
-      </c>
-      <c r="E7" t="n">
         <v>2025</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -23324,21 +23266,13 @@
         <v>45968</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
-      </c>
-      <c r="E8" t="n">
         <v>2025</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -23346,21 +23280,13 @@
         <v>45969</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
-      </c>
-      <c r="E9" t="n">
         <v>2025</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -23368,21 +23294,13 @@
         <v>45970</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
-      </c>
-      <c r="E10" t="n">
         <v>2025</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -23390,21 +23308,13 @@
         <v>45971</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
-      </c>
-      <c r="E11" t="n">
         <v>2025</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -23412,21 +23322,13 @@
         <v>45972</v>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
-      </c>
-      <c r="E12" t="n">
         <v>2025</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -23434,21 +23336,13 @@
         <v>45973</v>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
-      </c>
-      <c r="E13" t="n">
         <v>2025</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -23456,21 +23350,13 @@
         <v>45974</v>
       </c>
       <c r="B14" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
-      </c>
-      <c r="E14" t="n">
         <v>2025</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -23478,21 +23364,13 @@
         <v>45975</v>
       </c>
       <c r="B15" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
-      </c>
-      <c r="E15" t="n">
         <v>2025</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -23500,21 +23378,13 @@
         <v>45976</v>
       </c>
       <c r="B16" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
-      </c>
-      <c r="E16" t="n">
         <v>2025</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -23522,21 +23392,13 @@
         <v>45977</v>
       </c>
       <c r="B17" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
-      </c>
-      <c r="E17" t="n">
         <v>2025</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -23544,21 +23406,13 @@
         <v>45978</v>
       </c>
       <c r="B18" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
-      </c>
-      <c r="E18" t="n">
         <v>2025</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="19">
@@ -23566,21 +23420,13 @@
         <v>45979</v>
       </c>
       <c r="B19" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
-      </c>
-      <c r="E19" t="n">
         <v>2025</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="20">
@@ -23588,21 +23434,13 @@
         <v>45980</v>
       </c>
       <c r="B20" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" t="n">
         <v>2025</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="21">
@@ -23610,21 +23448,13 @@
         <v>45981</v>
       </c>
       <c r="B21" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
-      </c>
-      <c r="E21" t="n">
         <v>2025</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -23632,21 +23462,13 @@
         <v>45982</v>
       </c>
       <c r="B22" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
-      </c>
-      <c r="E22" t="n">
         <v>2025</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="23">
@@ -23654,21 +23476,13 @@
         <v>45983</v>
       </c>
       <c r="B23" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
-      </c>
-      <c r="E23" t="n">
         <v>2025</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="24">
@@ -23676,21 +23490,13 @@
         <v>45984</v>
       </c>
       <c r="B24" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
-      </c>
-      <c r="E24" t="n">
         <v>2025</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -23698,21 +23504,13 @@
         <v>45985</v>
       </c>
       <c r="B25" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
-      </c>
-      <c r="E25" t="n">
         <v>2025</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="26">
@@ -23720,21 +23518,13 @@
         <v>45986</v>
       </c>
       <c r="B26" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
-      </c>
-      <c r="E26" t="n">
         <v>2025</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="27">
@@ -23742,21 +23532,13 @@
         <v>45987</v>
       </c>
       <c r="B27" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
-      </c>
-      <c r="E27" t="n">
         <v>2025</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="28">
@@ -23764,21 +23546,13 @@
         <v>45988</v>
       </c>
       <c r="B28" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
-      </c>
-      <c r="E28" t="n">
         <v>2025</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="29">
@@ -23786,21 +23560,13 @@
         <v>45989</v>
       </c>
       <c r="B29" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
-      </c>
-      <c r="E29" t="n">
         <v>2025</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="30">
@@ -23808,21 +23574,13 @@
         <v>45990</v>
       </c>
       <c r="B30" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
-      </c>
-      <c r="E30" t="n">
         <v>2025</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="31">
@@ -23830,21 +23588,13 @@
         <v>45991</v>
       </c>
       <c r="B31" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
-      </c>
-      <c r="E31" t="n">
         <v>2025</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="32">
@@ -23852,21 +23602,13 @@
         <v>45992</v>
       </c>
       <c r="B32" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
-      </c>
-      <c r="E32" t="n">
         <v>2025</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="33">
@@ -23874,21 +23616,13 @@
         <v>45993</v>
       </c>
       <c r="B33" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D33" t="n">
-        <v>12</v>
-      </c>
-      <c r="E33" t="n">
         <v>2025</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="34">
@@ -23896,21 +23630,13 @@
         <v>45994</v>
       </c>
       <c r="B34" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>12</v>
-      </c>
-      <c r="E34" t="n">
         <v>2025</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="35">
@@ -23918,21 +23644,13 @@
         <v>45995</v>
       </c>
       <c r="B35" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D35" t="n">
-        <v>12</v>
-      </c>
-      <c r="E35" t="n">
         <v>2025</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="36">
@@ -23940,21 +23658,13 @@
         <v>45996</v>
       </c>
       <c r="B36" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
-      </c>
-      <c r="E36" t="n">
         <v>2025</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="37">
@@ -23962,21 +23672,13 @@
         <v>45997</v>
       </c>
       <c r="B37" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>12</v>
-      </c>
-      <c r="E37" t="n">
         <v>2025</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="38">
@@ -23984,21 +23686,13 @@
         <v>45998</v>
       </c>
       <c r="B38" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
-      </c>
-      <c r="E38" t="n">
         <v>2025</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="39">
@@ -24006,21 +23700,13 @@
         <v>45999</v>
       </c>
       <c r="B39" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D39" t="n">
-        <v>12</v>
-      </c>
-      <c r="E39" t="n">
         <v>2025</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="40">
@@ -24028,21 +23714,13 @@
         <v>46000</v>
       </c>
       <c r="B40" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D40" t="n">
-        <v>12</v>
-      </c>
-      <c r="E40" t="n">
         <v>2025</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="41">
@@ -24050,21 +23728,13 @@
         <v>46001</v>
       </c>
       <c r="B41" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
-        <v>12</v>
-      </c>
-      <c r="E41" t="n">
         <v>2025</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="42">
@@ -24072,21 +23742,13 @@
         <v>46002</v>
       </c>
       <c r="B42" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
-      </c>
-      <c r="E42" t="n">
         <v>2025</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="43">
@@ -24094,21 +23756,13 @@
         <v>46003</v>
       </c>
       <c r="B43" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D43" t="n">
-        <v>12</v>
-      </c>
-      <c r="E43" t="n">
         <v>2025</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="44">
@@ -24116,21 +23770,13 @@
         <v>46004</v>
       </c>
       <c r="B44" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D44" t="n">
-        <v>12</v>
-      </c>
-      <c r="E44" t="n">
         <v>2025</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="45">
@@ -24138,21 +23784,13 @@
         <v>46005</v>
       </c>
       <c r="B45" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
-      </c>
-      <c r="E45" t="n">
         <v>2025</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="46">
@@ -24160,21 +23798,13 @@
         <v>46006</v>
       </c>
       <c r="B46" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D46" t="n">
-        <v>12</v>
-      </c>
-      <c r="E46" t="n">
         <v>2025</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="47">
@@ -24182,21 +23812,13 @@
         <v>46007</v>
       </c>
       <c r="B47" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>12</v>
-      </c>
-      <c r="E47" t="n">
         <v>2025</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="48">
@@ -24204,21 +23826,13 @@
         <v>46008</v>
       </c>
       <c r="B48" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D48" t="n">
-        <v>12</v>
-      </c>
-      <c r="E48" t="n">
         <v>2025</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="49">
@@ -24226,21 +23840,13 @@
         <v>46009</v>
       </c>
       <c r="B49" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D49" t="n">
-        <v>12</v>
-      </c>
-      <c r="E49" t="n">
         <v>2025</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="50">
@@ -24248,21 +23854,13 @@
         <v>46010</v>
       </c>
       <c r="B50" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
-        <v>12</v>
-      </c>
-      <c r="E50" t="n">
         <v>2025</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="51">
@@ -24270,21 +23868,13 @@
         <v>46011</v>
       </c>
       <c r="B51" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D51" t="n">
-        <v>12</v>
-      </c>
-      <c r="E51" t="n">
         <v>2025</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="52">
@@ -24292,21 +23882,13 @@
         <v>46012</v>
       </c>
       <c r="B52" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D52" t="n">
-        <v>12</v>
-      </c>
-      <c r="E52" t="n">
         <v>2025</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="53">
@@ -24314,21 +23896,13 @@
         <v>46013</v>
       </c>
       <c r="B53" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D53" t="n">
-        <v>12</v>
-      </c>
-      <c r="E53" t="n">
         <v>2025</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="54">
@@ -24336,21 +23910,13 @@
         <v>46014</v>
       </c>
       <c r="B54" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>12</v>
-      </c>
-      <c r="E54" t="n">
         <v>2025</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="55">
@@ -24358,21 +23924,13 @@
         <v>46015</v>
       </c>
       <c r="B55" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
-      </c>
-      <c r="E55" t="n">
         <v>2025</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="56">
@@ -24380,21 +23938,13 @@
         <v>46016</v>
       </c>
       <c r="B56" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D56" t="n">
-        <v>12</v>
-      </c>
-      <c r="E56" t="n">
         <v>2025</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="57">
@@ -24402,21 +23952,13 @@
         <v>46017</v>
       </c>
       <c r="B57" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D57" t="n">
-        <v>12</v>
-      </c>
-      <c r="E57" t="n">
         <v>2025</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="58">
@@ -24424,21 +23966,13 @@
         <v>46018</v>
       </c>
       <c r="B58" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D58" t="n">
-        <v>12</v>
-      </c>
-      <c r="E58" t="n">
         <v>2025</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="59">
@@ -24446,21 +23980,13 @@
         <v>46019</v>
       </c>
       <c r="B59" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D59" t="n">
-        <v>12</v>
-      </c>
-      <c r="E59" t="n">
         <v>2025</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="60">
@@ -24468,21 +23994,13 @@
         <v>46020</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D60" t="n">
-        <v>12</v>
-      </c>
-      <c r="E60" t="n">
         <v>2025</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="61">
@@ -24490,21 +24008,13 @@
         <v>46021</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>12</v>
-      </c>
-      <c r="E61" t="n">
         <v>2025</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="62">
@@ -24512,21 +24022,13 @@
         <v>46022</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D62" t="n">
-        <v>12</v>
-      </c>
-      <c r="E62" t="n">
         <v>2025</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="63">
@@ -24534,21 +24036,13 @@
         <v>46023</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="n">
         <v>2026</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="64">
@@ -24556,21 +24050,13 @@
         <v>46024</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" t="n">
         <v>2026</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="65">
@@ -24578,21 +24064,13 @@
         <v>46025</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="n">
         <v>2026</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="66">
@@ -24600,21 +24078,13 @@
         <v>46026</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" t="n">
         <v>2026</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="67">
@@ -24622,21 +24092,13 @@
         <v>46027</v>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
         <v>2026</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="68">
@@ -24644,21 +24106,13 @@
         <v>46028</v>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="n">
         <v>2026</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="69">
@@ -24666,21 +24120,13 @@
         <v>46029</v>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="n">
         <v>2026</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="70">
@@ -24688,21 +24134,13 @@
         <v>46030</v>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" t="n">
         <v>2026</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="71">
@@ -24710,21 +24148,13 @@
         <v>46031</v>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" t="n">
         <v>2026</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="72">
@@ -24732,21 +24162,13 @@
         <v>46032</v>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C72" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" t="n">
         <v>2026</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="73">
@@ -24754,21 +24176,13 @@
         <v>46033</v>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C73" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
         <v>2026</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="74">
@@ -24776,21 +24190,13 @@
         <v>46034</v>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C74" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" t="n">
         <v>2026</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="75">
@@ -24798,21 +24204,13 @@
         <v>46035</v>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C75" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" t="n">
         <v>2026</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="76">
@@ -24820,21 +24218,13 @@
         <v>46036</v>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C76" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" t="n">
         <v>2026</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="77">
@@ -24842,21 +24232,13 @@
         <v>46037</v>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C77" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="n">
         <v>2026</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="78">
@@ -24864,21 +24246,13 @@
         <v>46038</v>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C78" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" t="n">
         <v>2026</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="79">
@@ -24886,21 +24260,13 @@
         <v>46039</v>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C79" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" t="n">
         <v>2026</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="80">
@@ -24908,21 +24274,13 @@
         <v>46040</v>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C80" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" t="n">
         <v>2026</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="81">
@@ -24930,21 +24288,13 @@
         <v>46041</v>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C81" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" t="n">
         <v>2026</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="82">
@@ -24952,21 +24302,13 @@
         <v>46042</v>
       </c>
       <c r="B82" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C82" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" t="n">
         <v>2026</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="83">
@@ -24974,21 +24316,13 @@
         <v>46043</v>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C83" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" t="n">
         <v>2026</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="84">
@@ -24996,21 +24330,13 @@
         <v>46044</v>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C84" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" t="n">
         <v>2026</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="85">
@@ -25018,21 +24344,13 @@
         <v>46045</v>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C85" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="n">
         <v>2026</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="86">
@@ -25040,21 +24358,13 @@
         <v>46046</v>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C86" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" t="n">
         <v>2026</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="87">
@@ -25062,21 +24372,13 @@
         <v>46047</v>
       </c>
       <c r="B87" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C87" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" t="n">
         <v>2026</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="88">
@@ -25084,21 +24386,13 @@
         <v>46048</v>
       </c>
       <c r="B88" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C88" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="n">
         <v>2026</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="89">
@@ -25106,21 +24400,13 @@
         <v>46049</v>
       </c>
       <c r="B89" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C89" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="n">
         <v>2026</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="90">
@@ -25128,21 +24414,13 @@
         <v>46050</v>
       </c>
       <c r="B90" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C90" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="n">
         <v>2026</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="91">
@@ -25150,21 +24428,13 @@
         <v>46051</v>
       </c>
       <c r="B91" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" t="n">
         <v>2026</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="92">
@@ -25172,21 +24442,13 @@
         <v>46052</v>
       </c>
       <c r="B92" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C92" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
         <v>2026</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="93">
@@ -25194,21 +24456,13 @@
         <v>46053</v>
       </c>
       <c r="B93" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C93" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" t="n">
         <v>2026</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="94">
@@ -25216,21 +24470,13 @@
         <v>46054</v>
       </c>
       <c r="B94" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C94" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
-      </c>
-      <c r="E94" t="n">
         <v>2026</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="95">
@@ -25238,21 +24484,13 @@
         <v>46055</v>
       </c>
       <c r="B95" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C95" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
-      </c>
-      <c r="E95" t="n">
         <v>2026</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="96">
@@ -25260,21 +24498,13 @@
         <v>46056</v>
       </c>
       <c r="B96" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C96" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
-      </c>
-      <c r="E96" t="n">
         <v>2026</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="97">
@@ -25282,21 +24512,13 @@
         <v>46057</v>
       </c>
       <c r="B97" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C97" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
-      </c>
-      <c r="E97" t="n">
         <v>2026</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="98">
@@ -25304,21 +24526,13 @@
         <v>46058</v>
       </c>
       <c r="B98" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C98" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
-      </c>
-      <c r="E98" t="n">
         <v>2026</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="99">
@@ -25326,21 +24540,13 @@
         <v>46059</v>
       </c>
       <c r="B99" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C99" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
-      </c>
-      <c r="E99" t="n">
         <v>2026</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="100">
@@ -25348,21 +24554,13 @@
         <v>46060</v>
       </c>
       <c r="B100" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C100" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
-      </c>
-      <c r="E100" t="n">
         <v>2026</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="101">
@@ -25370,21 +24568,13 @@
         <v>46061</v>
       </c>
       <c r="B101" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C101" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
-      </c>
-      <c r="E101" t="n">
         <v>2026</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="102">
@@ -25392,21 +24582,13 @@
         <v>46062</v>
       </c>
       <c r="B102" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C102" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" t="n">
         <v>2026</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="103">
@@ -25414,21 +24596,13 @@
         <v>46063</v>
       </c>
       <c r="B103" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C103" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
-      </c>
-      <c r="E103" t="n">
         <v>2026</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="104">
@@ -25436,21 +24610,13 @@
         <v>46064</v>
       </c>
       <c r="B104" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C104" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
-      </c>
-      <c r="E104" t="n">
         <v>2026</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="105">
@@ -25458,21 +24624,13 @@
         <v>46065</v>
       </c>
       <c r="B105" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C105" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E105" t="n">
         <v>2026</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="106">
@@ -25480,21 +24638,13 @@
         <v>46066</v>
       </c>
       <c r="B106" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C106" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
-      </c>
-      <c r="E106" t="n">
         <v>2026</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="107">
@@ -25502,21 +24652,13 @@
         <v>46067</v>
       </c>
       <c r="B107" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
-      </c>
-      <c r="E107" t="n">
         <v>2026</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="108">
@@ -25524,21 +24666,13 @@
         <v>46068</v>
       </c>
       <c r="B108" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
-      </c>
-      <c r="E108" t="n">
         <v>2026</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="109">
@@ -25546,21 +24680,13 @@
         <v>46069</v>
       </c>
       <c r="B109" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
-      </c>
-      <c r="E109" t="n">
         <v>2026</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="110">
@@ -25568,21 +24694,13 @@
         <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
-      </c>
-      <c r="E110" t="n">
         <v>2026</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="111">
@@ -25590,21 +24708,13 @@
         <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" t="n">
         <v>2026</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="112">
@@ -25612,21 +24722,13 @@
         <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
-      </c>
-      <c r="E112" t="n">
         <v>2026</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="113">
@@ -25634,21 +24736,13 @@
         <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
-      </c>
-      <c r="E113" t="n">
         <v>2026</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="114">
@@ -25656,21 +24750,13 @@
         <v>46074</v>
       </c>
       <c r="B114" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C114" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
-      </c>
-      <c r="E114" t="n">
         <v>2026</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="115">
@@ -25678,21 +24764,13 @@
         <v>46075</v>
       </c>
       <c r="B115" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C115" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
-      </c>
-      <c r="E115" t="n">
         <v>2026</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="116">
@@ -25700,21 +24778,13 @@
         <v>46076</v>
       </c>
       <c r="B116" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C116" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
-      </c>
-      <c r="E116" t="n">
         <v>2026</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="117">
@@ -25722,21 +24792,13 @@
         <v>46077</v>
       </c>
       <c r="B117" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C117" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
-      </c>
-      <c r="E117" t="n">
         <v>2026</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="118">
@@ -25744,21 +24806,13 @@
         <v>46078</v>
       </c>
       <c r="B118" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C118" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
-      </c>
-      <c r="E118" t="n">
         <v>2026</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="119">
@@ -25766,21 +24820,13 @@
         <v>46079</v>
       </c>
       <c r="B119" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C119" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
-      </c>
-      <c r="E119" t="n">
         <v>2026</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="120">
@@ -25788,21 +24834,13 @@
         <v>46080</v>
       </c>
       <c r="B120" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C120" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>2</v>
-      </c>
-      <c r="E120" t="n">
         <v>2026</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="121">
@@ -25810,21 +24848,13 @@
         <v>46081</v>
       </c>
       <c r="B121" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C121" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
-      </c>
-      <c r="E121" t="n">
         <v>2026</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="122">
@@ -25832,21 +24862,13 @@
         <v>46082</v>
       </c>
       <c r="B122" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C122" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
-      </c>
-      <c r="E122" t="n">
         <v>2026</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="123">
@@ -25854,21 +24876,13 @@
         <v>46083</v>
       </c>
       <c r="B123" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C123" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
-      </c>
-      <c r="E123" t="n">
         <v>2026</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="124">
@@ -25876,21 +24890,13 @@
         <v>46084</v>
       </c>
       <c r="B124" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C124" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
-      </c>
-      <c r="E124" t="n">
         <v>2026</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="125">
@@ -25898,21 +24904,13 @@
         <v>46085</v>
       </c>
       <c r="B125" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C125" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>3</v>
-      </c>
-      <c r="E125" t="n">
         <v>2026</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="126">
@@ -25920,21 +24918,13 @@
         <v>46086</v>
       </c>
       <c r="B126" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C126" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
-      </c>
-      <c r="E126" t="n">
         <v>2026</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="127">
@@ -25942,21 +24932,13 @@
         <v>46087</v>
       </c>
       <c r="B127" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C127" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
-      </c>
-      <c r="E127" t="n">
         <v>2026</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="128">
@@ -25964,21 +24946,13 @@
         <v>46088</v>
       </c>
       <c r="B128" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C128" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>3</v>
-      </c>
-      <c r="E128" t="n">
         <v>2026</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="129">
@@ -25986,21 +24960,13 @@
         <v>46089</v>
       </c>
       <c r="B129" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C129" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>3</v>
-      </c>
-      <c r="E129" t="n">
         <v>2026</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="130">
@@ -26008,21 +24974,13 @@
         <v>46090</v>
       </c>
       <c r="B130" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C130" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>3</v>
-      </c>
-      <c r="E130" t="n">
         <v>2026</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="131">
@@ -26030,21 +24988,13 @@
         <v>46091</v>
       </c>
       <c r="B131" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C131" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
-      </c>
-      <c r="E131" t="n">
         <v>2026</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="132">
@@ -26052,21 +25002,13 @@
         <v>46092</v>
       </c>
       <c r="B132" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C132" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>3</v>
-      </c>
-      <c r="E132" t="n">
         <v>2026</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="133">
@@ -26074,21 +25016,13 @@
         <v>46093</v>
       </c>
       <c r="B133" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C133" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>3</v>
-      </c>
-      <c r="E133" t="n">
         <v>2026</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="134">
@@ -26096,21 +25030,13 @@
         <v>46094</v>
       </c>
       <c r="B134" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C134" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>3</v>
-      </c>
-      <c r="E134" t="n">
         <v>2026</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="135">
@@ -26118,21 +25044,13 @@
         <v>46095</v>
       </c>
       <c r="B135" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C135" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>3</v>
-      </c>
-      <c r="E135" t="n">
         <v>2026</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="136">
@@ -26140,21 +25058,13 @@
         <v>46096</v>
       </c>
       <c r="B136" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C136" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
-      </c>
-      <c r="E136" t="n">
         <v>2026</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="137">
@@ -26162,21 +25072,13 @@
         <v>46097</v>
       </c>
       <c r="B137" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C137" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
-      </c>
-      <c r="E137" t="n">
         <v>2026</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="138">
@@ -26184,21 +25086,13 @@
         <v>46098</v>
       </c>
       <c r="B138" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C138" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
-      </c>
-      <c r="E138" t="n">
         <v>2026</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="139">
@@ -26206,21 +25100,13 @@
         <v>46099</v>
       </c>
       <c r="B139" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C139" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
-      </c>
-      <c r="E139" t="n">
         <v>2026</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="140">
@@ -26228,21 +25114,13 @@
         <v>46100</v>
       </c>
       <c r="B140" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C140" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>3</v>
-      </c>
-      <c r="E140" t="n">
         <v>2026</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="141">
@@ -26250,21 +25128,13 @@
         <v>46101</v>
       </c>
       <c r="B141" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C141" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
-      </c>
-      <c r="E141" t="n">
         <v>2026</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="142">
@@ -26272,21 +25142,13 @@
         <v>46102</v>
       </c>
       <c r="B142" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C142" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D142" t="n">
-        <v>3</v>
-      </c>
-      <c r="E142" t="n">
         <v>2026</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="143">
@@ -26294,21 +25156,13 @@
         <v>46103</v>
       </c>
       <c r="B143" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C143" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
-      </c>
-      <c r="E143" t="n">
         <v>2026</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="144">
@@ -26316,21 +25170,13 @@
         <v>46104</v>
       </c>
       <c r="B144" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C144" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>3</v>
-      </c>
-      <c r="E144" t="n">
         <v>2026</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="145">
@@ -26338,21 +25184,13 @@
         <v>46105</v>
       </c>
       <c r="B145" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C145" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>3</v>
-      </c>
-      <c r="E145" t="n">
         <v>2026</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="146">
@@ -26360,21 +25198,13 @@
         <v>46106</v>
       </c>
       <c r="B146" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C146" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D146" t="n">
-        <v>3</v>
-      </c>
-      <c r="E146" t="n">
         <v>2026</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="147">
@@ -26382,21 +25212,13 @@
         <v>46107</v>
       </c>
       <c r="B147" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C147" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>3</v>
-      </c>
-      <c r="E147" t="n">
         <v>2026</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="148">
@@ -26404,21 +25226,13 @@
         <v>46108</v>
       </c>
       <c r="B148" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C148" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
-      </c>
-      <c r="E148" t="n">
         <v>2026</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="149">
@@ -26426,21 +25240,13 @@
         <v>46109</v>
       </c>
       <c r="B149" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C149" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D149" t="n">
-        <v>3</v>
-      </c>
-      <c r="E149" t="n">
         <v>2026</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="150">
@@ -26448,21 +25254,13 @@
         <v>46110</v>
       </c>
       <c r="B150" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C150" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>3</v>
-      </c>
-      <c r="E150" t="n">
         <v>2026</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="151">
@@ -26470,21 +25268,13 @@
         <v>46111</v>
       </c>
       <c r="B151" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C151" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D151" t="n">
-        <v>3</v>
-      </c>
-      <c r="E151" t="n">
         <v>2026</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="152">
@@ -26492,21 +25282,13 @@
         <v>46112</v>
       </c>
       <c r="B152" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C152" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>3</v>
-      </c>
-      <c r="E152" t="n">
         <v>2026</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="153">
@@ -26514,21 +25296,13 @@
         <v>46113</v>
       </c>
       <c r="B153" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C153" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D153" t="n">
-        <v>4</v>
-      </c>
-      <c r="E153" t="n">
         <v>2026</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="154">
@@ -26536,21 +25310,13 @@
         <v>46114</v>
       </c>
       <c r="B154" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C154" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D154" t="n">
-        <v>4</v>
-      </c>
-      <c r="E154" t="n">
         <v>2026</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="155">
@@ -26558,21 +25324,13 @@
         <v>46115</v>
       </c>
       <c r="B155" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C155" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>4</v>
-      </c>
-      <c r="E155" t="n">
         <v>2026</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="156">
@@ -26580,21 +25338,13 @@
         <v>46116</v>
       </c>
       <c r="B156" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C156" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D156" t="n">
-        <v>4</v>
-      </c>
-      <c r="E156" t="n">
         <v>2026</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="157">
@@ -26602,21 +25352,13 @@
         <v>46117</v>
       </c>
       <c r="B157" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C157" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D157" t="n">
-        <v>4</v>
-      </c>
-      <c r="E157" t="n">
         <v>2026</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="158">
@@ -26624,21 +25366,13 @@
         <v>46118</v>
       </c>
       <c r="B158" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C158" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
-        <v>4</v>
-      </c>
-      <c r="E158" t="n">
         <v>2026</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="159">
@@ -26646,21 +25380,13 @@
         <v>46119</v>
       </c>
       <c r="B159" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C159" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D159" t="n">
-        <v>4</v>
-      </c>
-      <c r="E159" t="n">
         <v>2026</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="160">
@@ -26668,21 +25394,13 @@
         <v>46120</v>
       </c>
       <c r="B160" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C160" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D160" t="n">
-        <v>4</v>
-      </c>
-      <c r="E160" t="n">
         <v>2026</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="161">
@@ -26690,21 +25408,13 @@
         <v>46121</v>
       </c>
       <c r="B161" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C161" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D161" t="n">
-        <v>4</v>
-      </c>
-      <c r="E161" t="n">
         <v>2026</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="162">
@@ -26712,21 +25422,13 @@
         <v>46122</v>
       </c>
       <c r="B162" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C162" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D162" t="n">
-        <v>4</v>
-      </c>
-      <c r="E162" t="n">
         <v>2026</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="163">
@@ -26734,21 +25436,13 @@
         <v>46123</v>
       </c>
       <c r="B163" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C163" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D163" t="n">
-        <v>4</v>
-      </c>
-      <c r="E163" t="n">
         <v>2026</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="164">
@@ -26756,21 +25450,13 @@
         <v>46124</v>
       </c>
       <c r="B164" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C164" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>4</v>
-      </c>
-      <c r="E164" t="n">
         <v>2026</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="165">
@@ -26778,21 +25464,13 @@
         <v>46125</v>
       </c>
       <c r="B165" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C165" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>4</v>
-      </c>
-      <c r="E165" t="n">
         <v>2026</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="166">
@@ -26800,21 +25478,13 @@
         <v>46126</v>
       </c>
       <c r="B166" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C166" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D166" t="n">
-        <v>4</v>
-      </c>
-      <c r="E166" t="n">
         <v>2026</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="167">
@@ -26822,21 +25492,13 @@
         <v>46127</v>
       </c>
       <c r="B167" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C167" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D167" t="n">
-        <v>4</v>
-      </c>
-      <c r="E167" t="n">
         <v>2026</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="168">
@@ -26844,21 +25506,13 @@
         <v>46128</v>
       </c>
       <c r="B168" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C168" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D168" t="n">
-        <v>4</v>
-      </c>
-      <c r="E168" t="n">
         <v>2026</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="169">
@@ -26866,21 +25520,13 @@
         <v>46129</v>
       </c>
       <c r="B169" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C169" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D169" t="n">
-        <v>4</v>
-      </c>
-      <c r="E169" t="n">
         <v>2026</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="170">
@@ -26888,21 +25534,13 @@
         <v>46130</v>
       </c>
       <c r="B170" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C170" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D170" t="n">
-        <v>4</v>
-      </c>
-      <c r="E170" t="n">
         <v>2026</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="171">
@@ -26910,21 +25548,13 @@
         <v>46131</v>
       </c>
       <c r="B171" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C171" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D171" t="n">
-        <v>4</v>
-      </c>
-      <c r="E171" t="n">
         <v>2026</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="172">
@@ -26932,21 +25562,13 @@
         <v>46132</v>
       </c>
       <c r="B172" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C172" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D172" t="n">
-        <v>4</v>
-      </c>
-      <c r="E172" t="n">
         <v>2026</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="173">
@@ -26954,21 +25576,13 @@
         <v>46133</v>
       </c>
       <c r="B173" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C173" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D173" t="n">
-        <v>4</v>
-      </c>
-      <c r="E173" t="n">
         <v>2026</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="174">
@@ -26976,21 +25590,13 @@
         <v>46134</v>
       </c>
       <c r="B174" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C174" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D174" t="n">
-        <v>4</v>
-      </c>
-      <c r="E174" t="n">
         <v>2026</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="175">
@@ -26998,21 +25604,13 @@
         <v>46135</v>
       </c>
       <c r="B175" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C175" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D175" t="n">
-        <v>4</v>
-      </c>
-      <c r="E175" t="n">
         <v>2026</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
     <row r="176">
@@ -27020,21 +25618,13 @@
         <v>46136</v>
       </c>
       <c r="B176" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C176" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D176" t="n">
-        <v>4</v>
-      </c>
-      <c r="E176" t="n">
         <v>2026</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
       </c>
     </row>
     <row r="177">
@@ -27042,21 +25632,13 @@
         <v>46137</v>
       </c>
       <c r="B177" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C177" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D177" t="n">
-        <v>4</v>
-      </c>
-      <c r="E177" t="n">
         <v>2026</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
       </c>
     </row>
     <row r="178">
@@ -27064,21 +25646,13 @@
         <v>46138</v>
       </c>
       <c r="B178" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C178" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D178" t="n">
-        <v>4</v>
-      </c>
-      <c r="E178" t="n">
         <v>2026</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
       </c>
     </row>
     <row r="179">
@@ -27086,21 +25660,13 @@
         <v>46139</v>
       </c>
       <c r="B179" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C179" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D179" t="n">
-        <v>4</v>
-      </c>
-      <c r="E179" t="n">
         <v>2026</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
       </c>
     </row>
     <row r="180">
@@ -27108,21 +25674,13 @@
         <v>46140</v>
       </c>
       <c r="B180" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C180" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D180" t="n">
-        <v>4</v>
-      </c>
-      <c r="E180" t="n">
         <v>2026</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
       </c>
     </row>
     <row r="181">
@@ -27130,21 +25688,13 @@
         <v>46141</v>
       </c>
       <c r="B181" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C181" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D181" t="n">
-        <v>4</v>
-      </c>
-      <c r="E181" t="n">
         <v>2026</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
       </c>
     </row>
     <row r="182">
@@ -27152,21 +25702,13 @@
         <v>46142</v>
       </c>
       <c r="B182" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C182" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D182" t="n">
-        <v>4</v>
-      </c>
-      <c r="E182" t="n">
         <v>2026</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
       </c>
     </row>
   </sheetData>
